--- a/Data/Excel/map.xlsx
+++ b/Data/Excel/map.xlsx
@@ -225,7 +225,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>30950001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -244,7 +244,7 @@
         <v>300</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>30200001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -269,7 +269,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>30950002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -288,7 +288,7 @@
         <v>200</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>30200002</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -313,7 +313,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>30950003</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -332,7 +332,7 @@
         <v>500</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>30200003</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
